--- a/申請書/21機25萬範本.xlsx
+++ b/申請書/21機25萬範本.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/claude/申請書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\歸檔\21機25萬\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E78A1818-04F6-4A80-B6B0-5AF7E641323E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="1515" windowWidth="19350" windowHeight="13485" xr2:uid="{777809E9-0EF2-49B6-8099-4B6A7548F6F0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13875" windowHeight="8805"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -44,7 +43,7 @@
     <definedName name="澎湖縣">工作表3!$T$2:$T$39</definedName>
     <definedName name="機車">工作表2!$E$2:$E$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -65,13 +64,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>21世紀 馮盈瑛</author>
     <author>李志鴻</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{59893EE6-D7BA-4030-957F-36F467B6F422}">
+    <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{E3444EE7-0E3F-45C6-96CC-2FBE6BF8DD68}">
+    <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -108,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{A397FF1C-032C-47A7-B39D-C0B83CE629CB}">
+    <comment ref="C4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -171,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{0F1879EA-C7FD-4540-99CD-A2D68C438126}">
+    <comment ref="E4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -213,7 +212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{B8520E96-B7DE-479C-A6B6-21C4CBE6C512}">
+    <comment ref="F4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -227,7 +226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{244D3494-6766-48FE-81E4-6981CB3B8EF2}">
+    <comment ref="G4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -241,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J4" authorId="0" shapeId="0" xr:uid="{C99AB103-115D-4700-B252-870FB6900987}">
+    <comment ref="J4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -264,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{F94018EF-FA03-4915-A386-1819192054A7}">
+    <comment ref="C5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -287,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{794661F9-F01B-4C20-AEC9-D759E9A42E69}">
+    <comment ref="E5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -301,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{0EBFB1BC-FB32-4B27-AC74-6C04C2630C72}">
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -315,7 +314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{E404934D-EA5A-43FB-8C3A-129AF688F894}">
+    <comment ref="J5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -329,7 +328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{3A1A6F36-8DA2-4D8D-93FC-B65D04A53B37}">
+    <comment ref="C6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -353,7 +352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{516D68F8-D4EC-4D73-AED9-0671DDED365C}">
+    <comment ref="D6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -368,7 +367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{D12AABAE-CD44-4309-93D5-1401B7C3CE5A}">
+    <comment ref="E6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -383,7 +382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{C1E85708-73D5-407E-A818-5740BF82F139}">
+    <comment ref="C7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -407,7 +406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{9C5EB6B6-C97A-40A7-AE92-EF2BFD7D10A3}">
+    <comment ref="D7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -422,7 +421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{9EA250EC-20BB-4D5C-9DF5-0BB0E095A870}">
+    <comment ref="E7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -437,7 +436,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{6EEB8F57-A570-484B-B0CB-24588A54C430}">
+    <comment ref="E12" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>英文字請記得大寫</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -460,44 +473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{ED34B98B-C37B-4B7F-A318-19D3D25BAB7E}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t>英文字請記得大寫</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{C3EDFEAB-157D-44EE-AA30-3C18E1F925BE}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="細明體"/>
-            <family val="3"/>
-            <charset val="136"/>
-          </rPr>
-          <t>例</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 0938995559</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="1" shapeId="0" xr:uid="{5D69CB33-2F85-4204-8A6B-7A29C6807232}">
+    <comment ref="C13" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -543,7 +519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{F4981FAE-1EE8-4870-9B04-F3957E458F36}">
+    <comment ref="E13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -557,7 +533,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{1AC9D5E2-3372-480F-93F3-C17996CEADE3}">
+    <comment ref="F13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -571,7 +547,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{E6E3FAE0-1E72-47CB-96D6-7C8F0AA17732}">
+    <comment ref="G13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -585,7 +561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{A4E77E6C-68E7-4242-AAF9-64388EB1BB4C}">
+    <comment ref="J13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -608,10 +584,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{F0003A35-DB96-44B3-A444-96DC5599CD50}">
+    <comment ref="C14" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="細明體"/>
@@ -620,19 +597,9 @@
           </rPr>
           <t>縣市</t>
         </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{AB913FF5-C55B-4549-8719-2AD6342690FF}">
+    <comment ref="D14" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -647,7 +614,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{9AB3DE44-5F19-4C54-B2B5-4B33BFAF1DA6}">
+    <comment ref="E14" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -667,7 +634,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="503">
   <si>
     <t>是</t>
   </si>
@@ -759,6 +726,10 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
+    <t>月</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <t>保證人資料</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2172,87 +2143,96 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>月</t>
+    <t>年</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>非機車</t>
-  </si>
-  <si>
-    <t>3C家電</t>
-  </si>
-  <si>
-    <t>林宣宏</t>
+    <t>機車</t>
+  </si>
+  <si>
+    <t>中古車</t>
+  </si>
+  <si>
+    <t>0960700781</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>L124451250</t>
+    <t>066/11/19</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>083/07/02</t>
+    <t>096/01/31</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>108/12/20</t>
+    <t>南縣</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>補發</t>
-  </si>
-  <si>
-    <t>0967207727</t>
+    <t>臺南市</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>王福街2巷32弄23號</t>
+    <t>西庄126號</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>shasa814109@gmail.com</t>
+    <t>復興路511巷33號</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>台灣虎爺祖廟(義虎堂)</t>
+    <t>育宗企業</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>0426835908</t>
+    <t>0909582959</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>機動組 組長</t>
+    <t>0985537921</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1年</t>
+    <t>R222950015</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>林駿家</t>
+    <t>a0960700781@gmail.com</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>呂柏葳</t>
+    <t>066235200</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>0985419339</t>
+    <t>會計</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>0979311333</t>
+    <t>賴佳真</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳美蘭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>賴怡廷</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2367,13 +2347,6 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -2830,7 +2803,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2968,7 +2941,15 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3027,27 +3008,43 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="15" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3128,10 +3125,6 @@
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3147,7 +3140,14 @@
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE5E5"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3484,9 +3484,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B113EF-CCBD-476B-9470-1A2EBEC6D357}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -3495,199 +3495,201 @@
     <col min="5" max="5" width="15.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="5.5" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1"/>
     <col min="12" max="22" width="5.875" style="1" customWidth="1"/>
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21" thickBot="1">
+    <row r="1" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
-    <row r="2" spans="1:14" ht="18" customHeight="1" thickTop="1" thickBot="1">
+    <row r="2" spans="1:14" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="52"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="18" customHeight="1" thickTop="1">
+    <row r="3" spans="1:14" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="41" t="s">
-        <v>484</v>
+      <c r="C3" s="43" t="s">
+        <v>502</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="51" t="s">
-        <v>485</v>
-      </c>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54" t="s">
+      <c r="E3" s="53" t="s">
+        <v>496</v>
+      </c>
+      <c r="F3" s="54"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="55"/>
-      <c r="J3" s="56" t="s">
-        <v>489</v>
-      </c>
-      <c r="K3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58" t="s">
+        <v>486</v>
+      </c>
+      <c r="K3" s="59"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="18" customHeight="1">
+    <row r="4" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>37</v>
+        <v>489</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="H4" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="43"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="46" t="s">
+        <v>483</v>
+      </c>
+      <c r="K4" s="47"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="18" customHeight="1">
+    <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="9">
-        <v>120000</v>
+        <v>250000</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="6">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="58" t="s">
-        <v>482</v>
-      </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="62" t="s">
-        <v>483</v>
-      </c>
-      <c r="K5" s="63"/>
+      <c r="G5" s="63" t="s">
+        <v>484</v>
+      </c>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65" t="s">
+        <v>485</v>
+      </c>
+      <c r="K5" s="66"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" ht="18" customHeight="1">
+    <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>74</v>
+      <c r="C6" s="41" t="s">
+        <v>490</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>490</v>
-      </c>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="60"/>
+        <v>299</v>
+      </c>
+      <c r="E6" s="67" t="s">
+        <v>491</v>
+      </c>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" ht="18" customHeight="1">
+    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="58" t="s">
+      <c r="C7" s="42" t="s">
         <v>490</v>
       </c>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="60"/>
+      <c r="D7" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" s="67" t="s">
+        <v>492</v>
+      </c>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="69"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="18" customHeight="1" thickBot="1">
+    <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="64" t="s">
-        <v>491</v>
-      </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="66"/>
+      <c r="C8" s="70" t="s">
+        <v>497</v>
+      </c>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
       <c r="J8" s="11" t="s">
         <v>16</v>
       </c>
@@ -3698,105 +3700,107 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="18" customHeight="1" thickTop="1">
+    <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="58" t="s">
-        <v>492</v>
-      </c>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
+      <c r="C9" s="63" t="s">
+        <v>493</v>
+      </c>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
       <c r="F9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="56" t="s">
-        <v>493</v>
-      </c>
-      <c r="H9" s="57"/>
+      <c r="G9" s="63" t="s">
+        <v>498</v>
+      </c>
+      <c r="H9" s="64"/>
       <c r="I9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="67"/>
-      <c r="K9" s="68"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="74"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="18" customHeight="1" thickBot="1">
+    <row r="10" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="16">
-        <v>45000</v>
+        <v>35000</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>495</v>
+      <c r="G10" s="17">
+        <v>1</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I10" s="19"/>
-      <c r="J10" s="18"/>
+      <c r="J10" s="18" t="s">
+        <v>23</v>
+      </c>
       <c r="K10" s="20"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="18" customHeight="1" thickTop="1" thickBot="1">
+    <row r="11" spans="1:14" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="71"/>
+      <c r="B11" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="76"/>
+      <c r="K11" s="77"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:14" ht="18" thickTop="1" thickBot="1">
+    <row r="12" spans="1:14" ht="17.25" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="29"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="23" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="22"/>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="73"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="75"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="81"/>
       <c r="J12" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K12" s="25"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:14" ht="17.25" thickTop="1">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="26" t="s">
         <v>7</v>
@@ -3806,139 +3810,139 @@
         <v>8</v>
       </c>
       <c r="E13" s="8"/>
-      <c r="F13" s="6"/>
+      <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="76" t="s">
+      <c r="H13" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="77"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="47"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="60"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="62"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="1:14" ht="17.25" thickBot="1">
+    <row r="15" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
       <c r="F15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="44"/>
-      <c r="H15" s="86"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="60"/>
       <c r="I15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="68"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="74"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="1:14" ht="18" thickTop="1" thickBot="1">
+    <row r="16" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="88"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="88"/>
-      <c r="I16" s="88"/>
-      <c r="J16" s="88"/>
+      <c r="B16" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="93"/>
       <c r="K16" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
     </row>
-    <row r="17" spans="1:14" ht="18" thickTop="1" thickBot="1">
+    <row r="17" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="28" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D17" s="30" t="s">
         <v>1</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>447</v>
-      </c>
-      <c r="F17" s="78" t="s">
+        <v>448</v>
+      </c>
+      <c r="F17" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="79"/>
-      <c r="H17" s="80" t="s">
-        <v>498</v>
-      </c>
-      <c r="I17" s="81"/>
-      <c r="J17" s="82"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="86" t="s">
+        <v>494</v>
+      </c>
+      <c r="I17" s="87"/>
+      <c r="J17" s="88"/>
       <c r="K17" s="31" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
     </row>
-    <row r="18" spans="1:14" ht="18" thickTop="1" thickBot="1">
+    <row r="18" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="28" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D18" s="30" t="s">
         <v>1</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="F18" s="78" t="s">
+        <v>446</v>
+      </c>
+      <c r="F18" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="79"/>
-      <c r="H18" s="80" t="s">
-        <v>499</v>
-      </c>
-      <c r="I18" s="81"/>
-      <c r="J18" s="82"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="86" t="s">
+        <v>495</v>
+      </c>
+      <c r="I18" s="87"/>
+      <c r="J18" s="88"/>
       <c r="K18" s="31" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
     </row>
-    <row r="19" spans="1:14" ht="18" thickTop="1" thickBot="1">
+    <row r="19" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="28" t="s">
         <v>4</v>
@@ -3948,19 +3952,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="32"/>
-      <c r="F19" s="78" t="s">
+      <c r="F19" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="79"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="91"/>
       <c r="K19" s="31"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
     </row>
-    <row r="20" spans="1:14" ht="17.25" thickTop="1">
+    <row r="20" spans="1:14" ht="17.25" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3976,10 +3980,10 @@
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -3994,7 +3998,7 @@
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4010,7 +4014,7 @@
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4026,7 +4030,7 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4042,7 +4046,7 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -4058,7 +4062,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -4076,7 +4080,7 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="J3:K4 E5 G5:I5 E3:G4 C8:I8 C9:E9 C10 E10 J9:K9 K8 E12 H12:I12 K12 C13 E13:G13 C15:E15 G9:H10 C14:K14 C3:C7 D6:K7" name="input_19"/>
+    <protectedRange sqref="J3:K4 C3:C5 E5 G5:I5 E3:G4 C8:I8 C9:E9 C10 E10 G9:H10 J9:K9 K8 C12:C13 E12 H12:I12 E13:G13 K12 C6:K7" name="input_19"/>
     <protectedRange sqref="J5:K5" name="input"/>
   </protectedRanges>
   <mergeCells count="31">
@@ -4093,6 +4097,7 @@
     <mergeCell ref="E14:K14"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="E6:K6"/>
     <mergeCell ref="E7:K7"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="C9:E9"/>
@@ -4103,7 +4108,6 @@
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="J13:K13"/>
-    <mergeCell ref="E6:K6"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="B1:K1"/>
@@ -4113,70 +4117,75 @@
     <mergeCell ref="J3:K3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="H12 K12 E12:E13 C13 G13 J13">
+  <conditionalFormatting sqref="C12">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>"Rane(C12).Value&lt;&gt;"""""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12 K12 E12:E14 F13:G13 J13 C13:C14 D14">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>"C12&lt;&gt;"""""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:K5" xr:uid="{5766F727-7C16-4412-BC03-C6DD12A6D3AC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14 D6:D7">
+      <formula1>INDIRECT(C6)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:K5">
       <formula1>INDIRECT(G5)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D7 D14" xr:uid="{8E195D52-AC31-4741-8B58-E39402E6E6CF}">
-      <formula1>INDIRECT(C6)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" xr:uid="{6D34BBC9-3CBB-4E44-BCDE-8842E8FFEEAC}"/>
+    <hyperlink ref="C8" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CEE67518-77CB-44DB-B90B-36D26AE5AD80}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>工作表2!$A$2:$A$8</xm:f>
           </x14:formula1>
           <xm:sqref>E5</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5B1237E3-CED7-4A6D-AE7E-3F644D7FF206}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>工作表2!$B$2:$B$28</xm:f>
           </x14:formula1>
           <xm:sqref>F4 F13</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E24DFAC-0E85-4A41-9F71-1E1EE4C8791A}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>工作表2!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>G4 G13</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C206A7D5-6C7C-4237-9600-A7DDDEA5482F}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>工作表2!$D$2:$D$3</xm:f>
           </x14:formula1>
           <xm:sqref>G5:I5</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{92AC97C4-51C7-4398-B480-2A3BE0B8693F}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>工作表3!$A$1:$W$1</xm:f>
           </x14:formula1>
           <xm:sqref>C14 C6:C7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7EF46C55-383D-466F-809E-551C7AD75023}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>工作表2!$G$2:$G$3</xm:f>
           </x14:formula1>
           <xm:sqref>K8</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{17BAF83A-6D2B-4045-BD87-FD06E08C985F}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>工作表2!$H$2:$H$17</xm:f>
           </x14:formula1>
           <xm:sqref>K12 E17:E19</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{214F17FF-DCBF-42C8-B769-FF6572998C94}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>工作表2!$I$2:$I$3</xm:f>
           </x14:formula1>
@@ -4189,9 +4198,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC00FC89-BBE5-48AC-9838-8DC0E761D96B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.625" style="34" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9" style="34"/>
@@ -4201,283 +4210,283 @@
     <col min="9" max="16384" width="9" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" thickTop="1" thickBot="1">
+    <row r="1" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="34" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1" s="38" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="18" thickTop="1" thickBot="1">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34">
         <v>6</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="34" t="s">
-        <v>64</v>
-      </c>
       <c r="G2" s="34" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I2" s="40"/>
     </row>
-    <row r="3" spans="1:9" ht="17.25" thickTop="1">
+    <row r="3" spans="1:9" ht="17.25" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34">
         <v>12</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="I3" s="34" t="s">
         <v>461</v>
       </c>
-      <c r="G3" s="34" t="s">
-        <v>441</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>444</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="34">
         <v>18</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="34">
         <v>24</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="34">
         <v>30</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
         <v>36</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="34">
         <v>48</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4487,9 +4496,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E610743D-4695-4813-AA04-3A3332AEF494}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W39"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="11.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
@@ -4502,1261 +4511,1261 @@
     <col min="23" max="23" width="13.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2">
         <v>300</v>
       </c>
       <c r="E2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J2">
         <v>600</v>
       </c>
       <c r="K2" t="s">
+        <v>245</v>
+      </c>
+      <c r="L2" t="s">
+        <v>263</v>
+      </c>
+      <c r="M2" t="s">
+        <v>283</v>
+      </c>
+      <c r="N2" t="s">
+        <v>312</v>
+      </c>
+      <c r="O2" t="s">
+        <v>340</v>
+      </c>
+      <c r="P2" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>360</v>
+      </c>
+      <c r="R2" t="s">
+        <v>373</v>
+      </c>
+      <c r="S2" t="s">
+        <v>389</v>
+      </c>
+      <c r="T2" t="s">
+        <v>422</v>
+      </c>
+      <c r="U2" t="s">
+        <v>428</v>
+      </c>
+      <c r="V2" t="s">
+        <v>434</v>
+      </c>
+      <c r="W2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K3" t="s">
+        <v>246</v>
+      </c>
+      <c r="L3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N3" t="s">
+        <v>313</v>
+      </c>
+      <c r="O3" t="s">
+        <v>341</v>
+      </c>
+      <c r="P3" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>361</v>
+      </c>
+      <c r="R3" t="s">
+        <v>374</v>
+      </c>
+      <c r="S3" t="s">
+        <v>390</v>
+      </c>
+      <c r="T3" t="s">
+        <v>423</v>
+      </c>
+      <c r="U3" t="s">
+        <v>429</v>
+      </c>
+      <c r="V3" t="s">
+        <v>435</v>
+      </c>
+      <c r="W3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I4" t="s">
+        <v>234</v>
+      </c>
+      <c r="K4" t="s">
+        <v>247</v>
+      </c>
+      <c r="L4" t="s">
+        <v>265</v>
+      </c>
+      <c r="M4" t="s">
+        <v>285</v>
+      </c>
+      <c r="N4" t="s">
+        <v>314</v>
+      </c>
+      <c r="O4" t="s">
+        <v>342</v>
+      </c>
+      <c r="P4" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>362</v>
+      </c>
+      <c r="R4" t="s">
+        <v>375</v>
+      </c>
+      <c r="S4" t="s">
+        <v>391</v>
+      </c>
+      <c r="T4" t="s">
+        <v>424</v>
+      </c>
+      <c r="U4" t="s">
+        <v>430</v>
+      </c>
+      <c r="V4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" t="s">
+        <v>209</v>
+      </c>
+      <c r="I5" t="s">
+        <v>235</v>
+      </c>
+      <c r="K5" t="s">
+        <v>248</v>
+      </c>
+      <c r="L5" t="s">
+        <v>266</v>
+      </c>
+      <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
+        <v>315</v>
+      </c>
+      <c r="O5" t="s">
+        <v>343</v>
+      </c>
+      <c r="P5" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>363</v>
+      </c>
+      <c r="R5" t="s">
+        <v>376</v>
+      </c>
+      <c r="S5" t="s">
+        <v>392</v>
+      </c>
+      <c r="T5" t="s">
+        <v>425</v>
+      </c>
+      <c r="U5" t="s">
+        <v>431</v>
+      </c>
+      <c r="V5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H6" t="s">
+        <v>210</v>
+      </c>
+      <c r="I6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L6" t="s">
+        <v>267</v>
+      </c>
+      <c r="M6" t="s">
+        <v>287</v>
+      </c>
+      <c r="N6" t="s">
+        <v>316</v>
+      </c>
+      <c r="O6" t="s">
+        <v>344</v>
+      </c>
+      <c r="P6" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>364</v>
+      </c>
+      <c r="R6" t="s">
+        <v>377</v>
+      </c>
+      <c r="S6" t="s">
+        <v>393</v>
+      </c>
+      <c r="T6" t="s">
+        <v>426</v>
+      </c>
+      <c r="U6" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I7" t="s">
+        <v>237</v>
+      </c>
+      <c r="K7" t="s">
+        <v>250</v>
+      </c>
+      <c r="L7" t="s">
+        <v>268</v>
+      </c>
+      <c r="M7" t="s">
+        <v>288</v>
+      </c>
+      <c r="N7" t="s">
+        <v>317</v>
+      </c>
+      <c r="O7" t="s">
+        <v>345</v>
+      </c>
+      <c r="P7" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>365</v>
+      </c>
+      <c r="R7" t="s">
+        <v>378</v>
+      </c>
+      <c r="S7" t="s">
+        <v>394</v>
+      </c>
+      <c r="T7" t="s">
+        <v>427</v>
+      </c>
+      <c r="U7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" t="s">
+        <v>212</v>
+      </c>
+      <c r="I8" t="s">
+        <v>238</v>
+      </c>
+      <c r="K8" t="s">
+        <v>251</v>
+      </c>
+      <c r="L8" t="s">
+        <v>269</v>
+      </c>
+      <c r="M8" t="s">
+        <v>289</v>
+      </c>
+      <c r="N8" t="s">
+        <v>318</v>
+      </c>
+      <c r="O8" t="s">
+        <v>346</v>
+      </c>
+      <c r="P8" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>366</v>
+      </c>
+      <c r="R8" t="s">
+        <v>379</v>
+      </c>
+      <c r="S8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H9" t="s">
+        <v>213</v>
+      </c>
+      <c r="I9" t="s">
+        <v>239</v>
+      </c>
+      <c r="K9" t="s">
+        <v>252</v>
+      </c>
+      <c r="L9" t="s">
+        <v>270</v>
+      </c>
+      <c r="M9" t="s">
+        <v>290</v>
+      </c>
+      <c r="N9" t="s">
+        <v>319</v>
+      </c>
+      <c r="P9" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>367</v>
+      </c>
+      <c r="R9" t="s">
+        <v>380</v>
+      </c>
+      <c r="S9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H10" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" t="s">
+        <v>240</v>
+      </c>
+      <c r="K10" t="s">
+        <v>253</v>
+      </c>
+      <c r="L10" t="s">
+        <v>271</v>
+      </c>
+      <c r="M10" t="s">
+        <v>291</v>
+      </c>
+      <c r="N10" t="s">
+        <v>320</v>
+      </c>
+      <c r="P10" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>368</v>
+      </c>
+      <c r="R10" t="s">
+        <v>381</v>
+      </c>
+      <c r="S10" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" t="s">
+        <v>215</v>
+      </c>
+      <c r="I11" t="s">
+        <v>241</v>
+      </c>
+      <c r="K11" t="s">
+        <v>254</v>
+      </c>
+      <c r="L11" t="s">
+        <v>272</v>
+      </c>
+      <c r="M11" t="s">
+        <v>292</v>
+      </c>
+      <c r="N11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P11" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>369</v>
+      </c>
+      <c r="R11" t="s">
+        <v>382</v>
+      </c>
+      <c r="S11" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" t="s">
+        <v>216</v>
+      </c>
+      <c r="I12" t="s">
+        <v>242</v>
+      </c>
+      <c r="K12" t="s">
+        <v>255</v>
+      </c>
+      <c r="L12" t="s">
+        <v>273</v>
+      </c>
+      <c r="M12" t="s">
+        <v>293</v>
+      </c>
+      <c r="N12" t="s">
+        <v>322</v>
+      </c>
+      <c r="P12" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>370</v>
+      </c>
+      <c r="R12" t="s">
+        <v>383</v>
+      </c>
+      <c r="S12" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" t="s">
+        <v>188</v>
+      </c>
+      <c r="H13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I13" t="s">
+        <v>243</v>
+      </c>
+      <c r="K13" t="s">
+        <v>256</v>
+      </c>
+      <c r="L13" t="s">
+        <v>274</v>
+      </c>
+      <c r="M13" t="s">
+        <v>294</v>
+      </c>
+      <c r="N13" t="s">
+        <v>323</v>
+      </c>
+      <c r="P13" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>371</v>
+      </c>
+      <c r="R13" t="s">
+        <v>384</v>
+      </c>
+      <c r="S13" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" t="s">
+        <v>171</v>
+      </c>
+      <c r="G14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H14" t="s">
+        <v>218</v>
+      </c>
+      <c r="I14" t="s">
         <v>244</v>
       </c>
-      <c r="L2" t="s">
+      <c r="K14" t="s">
+        <v>257</v>
+      </c>
+      <c r="L14" t="s">
+        <v>275</v>
+      </c>
+      <c r="M14" t="s">
+        <v>295</v>
+      </c>
+      <c r="N14" t="s">
+        <v>324</v>
+      </c>
+      <c r="P14" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>372</v>
+      </c>
+      <c r="R14" t="s">
+        <v>385</v>
+      </c>
+      <c r="S14" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" t="s">
+        <v>172</v>
+      </c>
+      <c r="G15" t="s">
+        <v>190</v>
+      </c>
+      <c r="H15" t="s">
+        <v>219</v>
+      </c>
+      <c r="K15" t="s">
+        <v>258</v>
+      </c>
+      <c r="L15" t="s">
+        <v>276</v>
+      </c>
+      <c r="M15" t="s">
+        <v>296</v>
+      </c>
+      <c r="N15" t="s">
+        <v>325</v>
+      </c>
+      <c r="R15" t="s">
+        <v>386</v>
+      </c>
+      <c r="S15" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" t="s">
+        <v>191</v>
+      </c>
+      <c r="H16" t="s">
+        <v>220</v>
+      </c>
+      <c r="K16" t="s">
+        <v>259</v>
+      </c>
+      <c r="L16" t="s">
+        <v>277</v>
+      </c>
+      <c r="M16" t="s">
+        <v>297</v>
+      </c>
+      <c r="N16" t="s">
+        <v>481</v>
+      </c>
+      <c r="R16" t="s">
+        <v>387</v>
+      </c>
+      <c r="S16" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" t="s">
+        <v>221</v>
+      </c>
+      <c r="K17" t="s">
+        <v>260</v>
+      </c>
+      <c r="L17" t="s">
+        <v>278</v>
+      </c>
+      <c r="M17" t="s">
+        <v>298</v>
+      </c>
+      <c r="N17" t="s">
+        <v>326</v>
+      </c>
+      <c r="R17" t="s">
+        <v>388</v>
+      </c>
+      <c r="S17" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" t="s">
+        <v>175</v>
+      </c>
+      <c r="G18" t="s">
+        <v>193</v>
+      </c>
+      <c r="H18" t="s">
+        <v>222</v>
+      </c>
+      <c r="K18" t="s">
+        <v>261</v>
+      </c>
+      <c r="L18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M18" t="s">
+        <v>299</v>
+      </c>
+      <c r="N18" t="s">
+        <v>327</v>
+      </c>
+      <c r="S18" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" t="s">
+        <v>176</v>
+      </c>
+      <c r="G19" t="s">
+        <v>194</v>
+      </c>
+      <c r="H19" t="s">
+        <v>223</v>
+      </c>
+      <c r="K19" t="s">
         <v>262</v>
       </c>
-      <c r="M2" t="s">
+      <c r="L19" t="s">
+        <v>280</v>
+      </c>
+      <c r="M19" t="s">
+        <v>300</v>
+      </c>
+      <c r="N19" t="s">
+        <v>328</v>
+      </c>
+      <c r="S19" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" t="s">
+        <v>195</v>
+      </c>
+      <c r="H20" t="s">
+        <v>224</v>
+      </c>
+      <c r="L20" t="s">
+        <v>281</v>
+      </c>
+      <c r="M20" t="s">
+        <v>301</v>
+      </c>
+      <c r="N20" t="s">
+        <v>329</v>
+      </c>
+      <c r="S20" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>123</v>
+      </c>
+      <c r="G21" t="s">
+        <v>196</v>
+      </c>
+      <c r="H21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L21" t="s">
         <v>282</v>
       </c>
-      <c r="N2" t="s">
+      <c r="M21" t="s">
+        <v>302</v>
+      </c>
+      <c r="N21" t="s">
+        <v>330</v>
+      </c>
+      <c r="S21" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" t="s">
+        <v>197</v>
+      </c>
+      <c r="H22" t="s">
+        <v>226</v>
+      </c>
+      <c r="M22" t="s">
+        <v>303</v>
+      </c>
+      <c r="N22" t="s">
+        <v>331</v>
+      </c>
+      <c r="S22" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" t="s">
+        <v>198</v>
+      </c>
+      <c r="H23" t="s">
+        <v>227</v>
+      </c>
+      <c r="M23" t="s">
+        <v>304</v>
+      </c>
+      <c r="N23" t="s">
+        <v>332</v>
+      </c>
+      <c r="S23" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>126</v>
+      </c>
+      <c r="G24" t="s">
+        <v>199</v>
+      </c>
+      <c r="H24" t="s">
+        <v>228</v>
+      </c>
+      <c r="M24" t="s">
+        <v>305</v>
+      </c>
+      <c r="N24" t="s">
+        <v>333</v>
+      </c>
+      <c r="S24" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" t="s">
+        <v>229</v>
+      </c>
+      <c r="M25" t="s">
+        <v>306</v>
+      </c>
+      <c r="N25" t="s">
+        <v>334</v>
+      </c>
+      <c r="S25" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" t="s">
+        <v>201</v>
+      </c>
+      <c r="H26" t="s">
+        <v>230</v>
+      </c>
+      <c r="M26" t="s">
+        <v>307</v>
+      </c>
+      <c r="N26" t="s">
+        <v>335</v>
+      </c>
+      <c r="S26" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" t="s">
+        <v>202</v>
+      </c>
+      <c r="H27" t="s">
+        <v>231</v>
+      </c>
+      <c r="M27" t="s">
+        <v>308</v>
+      </c>
+      <c r="N27" t="s">
+        <v>336</v>
+      </c>
+      <c r="S27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" t="s">
+        <v>203</v>
+      </c>
+      <c r="M28" t="s">
+        <v>309</v>
+      </c>
+      <c r="N28" t="s">
+        <v>337</v>
+      </c>
+      <c r="S28" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>131</v>
+      </c>
+      <c r="G29" t="s">
+        <v>204</v>
+      </c>
+      <c r="M29" t="s">
+        <v>310</v>
+      </c>
+      <c r="N29" t="s">
+        <v>338</v>
+      </c>
+      <c r="S29" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>132</v>
+      </c>
+      <c r="G30" t="s">
+        <v>205</v>
+      </c>
+      <c r="M30" t="s">
         <v>311</v>
       </c>
-      <c r="O2" t="s">
+      <c r="N30" t="s">
         <v>339</v>
       </c>
-      <c r="P2" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>359</v>
-      </c>
-      <c r="R2" t="s">
-        <v>372</v>
-      </c>
-      <c r="S2" t="s">
-        <v>388</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="S30" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="M31" t="s">
+        <v>473</v>
+      </c>
+      <c r="N31" t="s">
+        <v>464</v>
+      </c>
+      <c r="S31" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="M32" t="s">
+        <v>474</v>
+      </c>
+      <c r="N32" t="s">
+        <v>466</v>
+      </c>
+      <c r="S32" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="33" spans="13:19" x14ac:dyDescent="0.25">
+      <c r="M33" t="s">
+        <v>475</v>
+      </c>
+      <c r="N33" t="s">
+        <v>465</v>
+      </c>
+      <c r="S33" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="34" spans="13:19" x14ac:dyDescent="0.25">
+      <c r="M34" t="s">
+        <v>476</v>
+      </c>
+      <c r="N34" t="s">
+        <v>467</v>
+      </c>
+      <c r="S34" t="s">
         <v>421</v>
       </c>
-      <c r="U2" t="s">
-        <v>427</v>
-      </c>
-      <c r="V2" t="s">
-        <v>433</v>
-      </c>
-      <c r="W2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H3" t="s">
-        <v>206</v>
-      </c>
-      <c r="I3" t="s">
-        <v>232</v>
-      </c>
-      <c r="K3" t="s">
-        <v>245</v>
-      </c>
-      <c r="L3" t="s">
-        <v>263</v>
-      </c>
-      <c r="M3" t="s">
-        <v>283</v>
-      </c>
-      <c r="N3" t="s">
-        <v>312</v>
-      </c>
-      <c r="O3" t="s">
-        <v>340</v>
-      </c>
-      <c r="P3" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>360</v>
-      </c>
-      <c r="R3" t="s">
-        <v>373</v>
-      </c>
-      <c r="S3" t="s">
-        <v>389</v>
-      </c>
-      <c r="T3" t="s">
-        <v>422</v>
-      </c>
-      <c r="U3" t="s">
-        <v>428</v>
-      </c>
-      <c r="V3" t="s">
-        <v>434</v>
-      </c>
-      <c r="W3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
-      <c r="A4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" t="s">
-        <v>207</v>
-      </c>
-      <c r="I4" t="s">
-        <v>233</v>
-      </c>
-      <c r="K4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L4" t="s">
-        <v>264</v>
-      </c>
-      <c r="M4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N4" t="s">
-        <v>313</v>
-      </c>
-      <c r="O4" t="s">
-        <v>341</v>
-      </c>
-      <c r="P4" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>361</v>
-      </c>
-      <c r="R4" t="s">
-        <v>374</v>
-      </c>
-      <c r="S4" t="s">
-        <v>390</v>
-      </c>
-      <c r="T4" t="s">
-        <v>423</v>
-      </c>
-      <c r="U4" t="s">
-        <v>429</v>
-      </c>
-      <c r="V4" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
-      <c r="A5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" t="s">
-        <v>179</v>
-      </c>
-      <c r="H5" t="s">
-        <v>208</v>
-      </c>
-      <c r="I5" t="s">
-        <v>234</v>
-      </c>
-      <c r="K5" t="s">
-        <v>247</v>
-      </c>
-      <c r="L5" t="s">
-        <v>265</v>
-      </c>
-      <c r="M5" t="s">
-        <v>285</v>
-      </c>
-      <c r="N5" t="s">
-        <v>314</v>
-      </c>
-      <c r="O5" t="s">
-        <v>342</v>
-      </c>
-      <c r="P5" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>362</v>
-      </c>
-      <c r="R5" t="s">
-        <v>375</v>
-      </c>
-      <c r="S5" t="s">
-        <v>391</v>
-      </c>
-      <c r="T5" t="s">
-        <v>424</v>
-      </c>
-      <c r="U5" t="s">
-        <v>430</v>
-      </c>
-      <c r="V5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" t="s">
-        <v>162</v>
-      </c>
-      <c r="G6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H6" t="s">
-        <v>209</v>
-      </c>
-      <c r="I6" t="s">
-        <v>235</v>
-      </c>
-      <c r="K6" t="s">
-        <v>248</v>
-      </c>
-      <c r="L6" t="s">
-        <v>266</v>
-      </c>
-      <c r="M6" t="s">
-        <v>286</v>
-      </c>
-      <c r="N6" t="s">
-        <v>315</v>
-      </c>
-      <c r="O6" t="s">
-        <v>343</v>
-      </c>
-      <c r="P6" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>363</v>
-      </c>
-      <c r="R6" t="s">
-        <v>376</v>
-      </c>
-      <c r="S6" t="s">
-        <v>392</v>
-      </c>
-      <c r="T6" t="s">
-        <v>425</v>
-      </c>
-      <c r="U6" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F7" t="s">
-        <v>163</v>
-      </c>
-      <c r="G7" t="s">
-        <v>181</v>
-      </c>
-      <c r="H7" t="s">
-        <v>210</v>
-      </c>
-      <c r="I7" t="s">
-        <v>236</v>
-      </c>
-      <c r="K7" t="s">
-        <v>249</v>
-      </c>
-      <c r="L7" t="s">
-        <v>267</v>
-      </c>
-      <c r="M7" t="s">
-        <v>287</v>
-      </c>
-      <c r="N7" t="s">
-        <v>316</v>
-      </c>
-      <c r="O7" t="s">
-        <v>344</v>
-      </c>
-      <c r="P7" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>364</v>
-      </c>
-      <c r="R7" t="s">
-        <v>377</v>
-      </c>
-      <c r="S7" t="s">
-        <v>393</v>
-      </c>
-      <c r="T7" t="s">
-        <v>426</v>
-      </c>
-      <c r="U7" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F8" t="s">
-        <v>164</v>
-      </c>
-      <c r="G8" t="s">
-        <v>182</v>
-      </c>
-      <c r="H8" t="s">
-        <v>211</v>
-      </c>
-      <c r="I8" t="s">
-        <v>237</v>
-      </c>
-      <c r="K8" t="s">
-        <v>250</v>
-      </c>
-      <c r="L8" t="s">
-        <v>268</v>
-      </c>
-      <c r="M8" t="s">
-        <v>288</v>
-      </c>
-      <c r="N8" t="s">
-        <v>317</v>
-      </c>
-      <c r="O8" t="s">
-        <v>345</v>
-      </c>
-      <c r="P8" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>365</v>
-      </c>
-      <c r="R8" t="s">
-        <v>378</v>
-      </c>
-      <c r="S8" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F9" t="s">
-        <v>165</v>
-      </c>
-      <c r="G9" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" t="s">
-        <v>212</v>
-      </c>
-      <c r="I9" t="s">
-        <v>238</v>
-      </c>
-      <c r="K9" t="s">
-        <v>251</v>
-      </c>
-      <c r="L9" t="s">
-        <v>269</v>
-      </c>
-      <c r="M9" t="s">
-        <v>289</v>
-      </c>
-      <c r="N9" t="s">
-        <v>318</v>
-      </c>
-      <c r="P9" t="s">
-        <v>353</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>366</v>
-      </c>
-      <c r="R9" t="s">
-        <v>379</v>
-      </c>
-      <c r="S9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F10" t="s">
-        <v>166</v>
-      </c>
-      <c r="G10" t="s">
-        <v>184</v>
-      </c>
-      <c r="H10" t="s">
-        <v>213</v>
-      </c>
-      <c r="I10" t="s">
-        <v>239</v>
-      </c>
-      <c r="K10" t="s">
-        <v>252</v>
-      </c>
-      <c r="L10" t="s">
-        <v>270</v>
-      </c>
-      <c r="M10" t="s">
-        <v>290</v>
-      </c>
-      <c r="N10" t="s">
-        <v>319</v>
-      </c>
-      <c r="P10" t="s">
-        <v>354</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>367</v>
-      </c>
-      <c r="R10" t="s">
-        <v>380</v>
-      </c>
-      <c r="S10" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
-      <c r="A11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" t="s">
-        <v>154</v>
-      </c>
-      <c r="F11" t="s">
-        <v>167</v>
-      </c>
-      <c r="G11" t="s">
-        <v>185</v>
-      </c>
-      <c r="H11" t="s">
-        <v>214</v>
-      </c>
-      <c r="I11" t="s">
-        <v>240</v>
-      </c>
-      <c r="K11" t="s">
-        <v>253</v>
-      </c>
-      <c r="L11" t="s">
-        <v>271</v>
-      </c>
-      <c r="M11" t="s">
-        <v>291</v>
-      </c>
-      <c r="N11" t="s">
-        <v>320</v>
-      </c>
-      <c r="P11" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>368</v>
-      </c>
-      <c r="R11" t="s">
-        <v>381</v>
-      </c>
-      <c r="S11" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
-      <c r="A12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" t="s">
-        <v>168</v>
-      </c>
-      <c r="G12" t="s">
-        <v>186</v>
-      </c>
-      <c r="H12" t="s">
-        <v>215</v>
-      </c>
-      <c r="I12" t="s">
-        <v>241</v>
-      </c>
-      <c r="K12" t="s">
-        <v>254</v>
-      </c>
-      <c r="L12" t="s">
-        <v>272</v>
-      </c>
-      <c r="M12" t="s">
-        <v>292</v>
-      </c>
-      <c r="N12" t="s">
-        <v>321</v>
-      </c>
-      <c r="P12" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>369</v>
-      </c>
-      <c r="R12" t="s">
-        <v>382</v>
-      </c>
-      <c r="S12" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23">
-      <c r="A13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" t="s">
-        <v>169</v>
-      </c>
-      <c r="G13" t="s">
-        <v>187</v>
-      </c>
-      <c r="H13" t="s">
-        <v>216</v>
-      </c>
-      <c r="I13" t="s">
-        <v>242</v>
-      </c>
-      <c r="K13" t="s">
-        <v>255</v>
-      </c>
-      <c r="L13" t="s">
-        <v>273</v>
-      </c>
-      <c r="M13" t="s">
-        <v>293</v>
-      </c>
-      <c r="N13" t="s">
-        <v>322</v>
-      </c>
-      <c r="P13" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>370</v>
-      </c>
-      <c r="R13" t="s">
-        <v>383</v>
-      </c>
-      <c r="S13" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23">
-      <c r="B14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" t="s">
-        <v>157</v>
-      </c>
-      <c r="F14" t="s">
-        <v>170</v>
-      </c>
-      <c r="G14" t="s">
-        <v>188</v>
-      </c>
-      <c r="H14" t="s">
-        <v>217</v>
-      </c>
-      <c r="I14" t="s">
-        <v>243</v>
-      </c>
-      <c r="K14" t="s">
-        <v>256</v>
-      </c>
-      <c r="L14" t="s">
-        <v>274</v>
-      </c>
-      <c r="M14" t="s">
-        <v>294</v>
-      </c>
-      <c r="N14" t="s">
-        <v>323</v>
-      </c>
-      <c r="P14" t="s">
-        <v>358</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>371</v>
-      </c>
-      <c r="R14" t="s">
-        <v>384</v>
-      </c>
-      <c r="S14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23">
-      <c r="B15" t="s">
-        <v>116</v>
-      </c>
-      <c r="F15" t="s">
-        <v>171</v>
-      </c>
-      <c r="G15" t="s">
-        <v>189</v>
-      </c>
-      <c r="H15" t="s">
-        <v>218</v>
-      </c>
-      <c r="K15" t="s">
-        <v>257</v>
-      </c>
-      <c r="L15" t="s">
-        <v>275</v>
-      </c>
-      <c r="M15" t="s">
-        <v>295</v>
-      </c>
-      <c r="N15" t="s">
-        <v>324</v>
-      </c>
-      <c r="R15" t="s">
-        <v>385</v>
-      </c>
-      <c r="S15" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23">
-      <c r="B16" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" t="s">
-        <v>172</v>
-      </c>
-      <c r="G16" t="s">
-        <v>190</v>
-      </c>
-      <c r="H16" t="s">
-        <v>219</v>
-      </c>
-      <c r="K16" t="s">
-        <v>258</v>
-      </c>
-      <c r="L16" t="s">
-        <v>276</v>
-      </c>
-      <c r="M16" t="s">
-        <v>296</v>
-      </c>
-      <c r="N16" t="s">
+    </row>
+    <row r="35" spans="13:19" x14ac:dyDescent="0.25">
+      <c r="M35" t="s">
+        <v>477</v>
+      </c>
+      <c r="N35" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="36" spans="13:19" x14ac:dyDescent="0.25">
+      <c r="M36" t="s">
+        <v>478</v>
+      </c>
+      <c r="N36" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="37" spans="13:19" x14ac:dyDescent="0.25">
+      <c r="M37" t="s">
+        <v>479</v>
+      </c>
+      <c r="N37" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="38" spans="13:19" x14ac:dyDescent="0.25">
+      <c r="M38" t="s">
         <v>480</v>
       </c>
-      <c r="R16" t="s">
-        <v>386</v>
-      </c>
-      <c r="S16" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="17" spans="2:19">
-      <c r="B17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" t="s">
-        <v>173</v>
-      </c>
-      <c r="G17" t="s">
-        <v>191</v>
-      </c>
-      <c r="H17" t="s">
-        <v>220</v>
-      </c>
-      <c r="K17" t="s">
-        <v>259</v>
-      </c>
-      <c r="L17" t="s">
-        <v>277</v>
-      </c>
-      <c r="M17" t="s">
-        <v>297</v>
-      </c>
-      <c r="N17" t="s">
-        <v>325</v>
-      </c>
-      <c r="R17" t="s">
-        <v>387</v>
-      </c>
-      <c r="S17" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="18" spans="2:19">
-      <c r="B18" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" t="s">
-        <v>174</v>
-      </c>
-      <c r="G18" t="s">
-        <v>192</v>
-      </c>
-      <c r="H18" t="s">
-        <v>221</v>
-      </c>
-      <c r="K18" t="s">
-        <v>260</v>
-      </c>
-      <c r="L18" t="s">
-        <v>278</v>
-      </c>
-      <c r="M18" t="s">
-        <v>298</v>
-      </c>
-      <c r="N18" t="s">
-        <v>326</v>
-      </c>
-      <c r="S18" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="19" spans="2:19">
-      <c r="B19" t="s">
-        <v>120</v>
-      </c>
-      <c r="F19" t="s">
-        <v>175</v>
-      </c>
-      <c r="G19" t="s">
-        <v>193</v>
-      </c>
-      <c r="H19" t="s">
-        <v>222</v>
-      </c>
-      <c r="K19" t="s">
-        <v>261</v>
-      </c>
-      <c r="L19" t="s">
-        <v>279</v>
-      </c>
-      <c r="M19" t="s">
-        <v>299</v>
-      </c>
-      <c r="N19" t="s">
-        <v>327</v>
-      </c>
-      <c r="S19" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="20" spans="2:19">
-      <c r="B20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" t="s">
-        <v>194</v>
-      </c>
-      <c r="H20" t="s">
-        <v>223</v>
-      </c>
-      <c r="L20" t="s">
-        <v>280</v>
-      </c>
-      <c r="M20" t="s">
-        <v>300</v>
-      </c>
-      <c r="N20" t="s">
-        <v>328</v>
-      </c>
-      <c r="S20" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="21" spans="2:19">
-      <c r="B21" t="s">
-        <v>122</v>
-      </c>
-      <c r="G21" t="s">
-        <v>195</v>
-      </c>
-      <c r="H21" t="s">
-        <v>224</v>
-      </c>
-      <c r="L21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M21" t="s">
-        <v>301</v>
-      </c>
-      <c r="N21" t="s">
-        <v>329</v>
-      </c>
-      <c r="S21" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="22" spans="2:19">
-      <c r="B22" t="s">
-        <v>123</v>
-      </c>
-      <c r="G22" t="s">
-        <v>196</v>
-      </c>
-      <c r="H22" t="s">
-        <v>225</v>
-      </c>
-      <c r="M22" t="s">
-        <v>302</v>
-      </c>
-      <c r="N22" t="s">
-        <v>330</v>
-      </c>
-      <c r="S22" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="23" spans="2:19">
-      <c r="B23" t="s">
-        <v>124</v>
-      </c>
-      <c r="G23" t="s">
-        <v>197</v>
-      </c>
-      <c r="H23" t="s">
-        <v>226</v>
-      </c>
-      <c r="M23" t="s">
-        <v>303</v>
-      </c>
-      <c r="N23" t="s">
-        <v>331</v>
-      </c>
-      <c r="S23" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="24" spans="2:19">
-      <c r="B24" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" t="s">
-        <v>198</v>
-      </c>
-      <c r="H24" t="s">
-        <v>227</v>
-      </c>
-      <c r="M24" t="s">
-        <v>304</v>
-      </c>
-      <c r="N24" t="s">
-        <v>332</v>
-      </c>
-      <c r="S24" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="25" spans="2:19">
-      <c r="B25" t="s">
-        <v>126</v>
-      </c>
-      <c r="G25" t="s">
-        <v>199</v>
-      </c>
-      <c r="H25" t="s">
-        <v>228</v>
-      </c>
-      <c r="M25" t="s">
-        <v>305</v>
-      </c>
-      <c r="N25" t="s">
-        <v>333</v>
-      </c>
-      <c r="S25" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="26" spans="2:19">
-      <c r="B26" t="s">
-        <v>127</v>
-      </c>
-      <c r="G26" t="s">
-        <v>200</v>
-      </c>
-      <c r="H26" t="s">
-        <v>229</v>
-      </c>
-      <c r="M26" t="s">
-        <v>306</v>
-      </c>
-      <c r="N26" t="s">
-        <v>334</v>
-      </c>
-      <c r="S26" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="27" spans="2:19">
-      <c r="B27" t="s">
-        <v>128</v>
-      </c>
-      <c r="G27" t="s">
-        <v>201</v>
-      </c>
-      <c r="H27" t="s">
-        <v>230</v>
-      </c>
-      <c r="M27" t="s">
-        <v>307</v>
-      </c>
-      <c r="N27" t="s">
-        <v>335</v>
-      </c>
-      <c r="S27" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="28" spans="2:19">
-      <c r="B28" t="s">
-        <v>129</v>
-      </c>
-      <c r="G28" t="s">
-        <v>202</v>
-      </c>
-      <c r="M28" t="s">
-        <v>308</v>
-      </c>
-      <c r="N28" t="s">
-        <v>336</v>
-      </c>
-      <c r="S28" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="29" spans="2:19">
-      <c r="B29" t="s">
-        <v>130</v>
-      </c>
-      <c r="G29" t="s">
-        <v>203</v>
-      </c>
-      <c r="M29" t="s">
-        <v>309</v>
-      </c>
-      <c r="N29" t="s">
-        <v>337</v>
-      </c>
-      <c r="S29" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="30" spans="2:19">
-      <c r="B30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G30" t="s">
-        <v>204</v>
-      </c>
-      <c r="M30" t="s">
-        <v>310</v>
-      </c>
-      <c r="N30" t="s">
-        <v>338</v>
-      </c>
-      <c r="S30" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="31" spans="2:19">
-      <c r="M31" t="s">
+      <c r="N38" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="39" spans="13:19" x14ac:dyDescent="0.25">
+      <c r="N39" t="s">
         <v>472</v>
-      </c>
-      <c r="N31" t="s">
-        <v>463</v>
-      </c>
-      <c r="S31" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="32" spans="2:19">
-      <c r="M32" t="s">
-        <v>473</v>
-      </c>
-      <c r="N32" t="s">
-        <v>465</v>
-      </c>
-      <c r="S32" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="33" spans="13:19">
-      <c r="M33" t="s">
-        <v>474</v>
-      </c>
-      <c r="N33" t="s">
-        <v>464</v>
-      </c>
-      <c r="S33" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="34" spans="13:19">
-      <c r="M34" t="s">
-        <v>475</v>
-      </c>
-      <c r="N34" t="s">
-        <v>466</v>
-      </c>
-      <c r="S34" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="35" spans="13:19">
-      <c r="M35" t="s">
-        <v>476</v>
-      </c>
-      <c r="N35" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="36" spans="13:19">
-      <c r="M36" t="s">
-        <v>477</v>
-      </c>
-      <c r="N36" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="37" spans="13:19">
-      <c r="M37" t="s">
-        <v>478</v>
-      </c>
-      <c r="N37" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="38" spans="13:19">
-      <c r="M38" t="s">
-        <v>479</v>
-      </c>
-      <c r="N38" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="39" spans="13:19">
-      <c r="N39" t="s">
-        <v>471</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:W1" xr:uid="{F184DDFA-DF4B-4557-93E6-92220003235C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:W1">
       <formula1>$A$1:$W$1</formula1>
     </dataValidation>
   </dataValidations>

--- a/申請書/21機25萬範本.xlsx
+++ b/申請書/21機25萬範本.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\歸檔\21機25萬\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/claude/申請書/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_E23DF245F06FDDA53B91ADE0BADE912E6BE4799E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF0368EA-D049-498A-9DD5-CD62FC273BA0}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13875" windowHeight="8805"/>
+    <workbookView xWindow="9510" yWindow="1995" windowWidth="17340" windowHeight="13485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -48,29 +49,18 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>21世紀 馮盈瑛</author>
     <author>李志鴻</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0" shapeId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -84,7 +74,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -107,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C4" authorId="0" shapeId="0">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -170,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E4" authorId="0" shapeId="0">
+    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -212,7 +202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -226,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -240,7 +230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J4" authorId="0" shapeId="0">
+    <comment ref="J4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -263,7 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -286,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -300,7 +290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -314,7 +304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0">
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -328,7 +318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C6" authorId="0" shapeId="0">
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -352,7 +342,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -367,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -382,7 +372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C7" authorId="0" shapeId="0">
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -406,7 +396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -421,7 +411,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -436,7 +426,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -450,7 +440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0">
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -473,7 +463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C13" authorId="1" shapeId="0">
+    <comment ref="C13" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -519,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0">
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -533,7 +523,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -547,7 +537,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0">
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
       <text>
         <r>
           <rPr>
@@ -561,7 +551,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0">
+    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
       <text>
         <r>
           <rPr>
@@ -584,7 +574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C14" authorId="1" shapeId="0">
+    <comment ref="C14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
       <text>
         <r>
           <rPr>
@@ -599,7 +589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="1" shapeId="0">
+    <comment ref="D14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -614,7 +604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="1" shapeId="0">
+    <comment ref="E14" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -634,7 +624,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="502">
   <si>
     <t>是</t>
   </si>
@@ -2145,10 +2135,6 @@
   <si>
     <t>年</t>
     <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>機車</t>
@@ -2228,7 +2214,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
@@ -2803,7 +2789,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2941,75 +2927,62 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="11" fillId="10" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="10" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
@@ -3060,14 +3033,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3097,42 +3062,55 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="10" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="10" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3484,7 +3462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3504,36 +3482,36 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="52"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="84"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -3543,25 +3521,25 @@
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="43" t="s">
-        <v>502</v>
+      <c r="C3" s="41" t="s">
+        <v>501</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="53" t="s">
-        <v>496</v>
-      </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="56" t="s">
+      <c r="E3" s="85" t="s">
+        <v>495</v>
+      </c>
+      <c r="F3" s="86"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58" t="s">
-        <v>486</v>
-      </c>
-      <c r="K3" s="59"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="90" t="s">
+        <v>485</v>
+      </c>
+      <c r="K3" s="91"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -3572,28 +3550,26 @@
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>488</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>489</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="45"/>
-      <c r="J4" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="K4" s="47"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="77"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -3615,15 +3591,15 @@
       <c r="F5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="63" t="s">
+      <c r="G5" s="58" t="s">
+        <v>483</v>
+      </c>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="60" t="s">
         <v>484</v>
       </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65" t="s">
-        <v>485</v>
-      </c>
-      <c r="K5" s="66"/>
+      <c r="K5" s="61"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -3633,21 +3609,21 @@
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="41" t="s">
-        <v>490</v>
+      <c r="C6" s="6" t="s">
+        <v>489</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="E6" s="67" t="s">
-        <v>491</v>
-      </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="69"/>
+      <c r="E6" s="62" t="s">
+        <v>490</v>
+      </c>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -3657,21 +3633,21 @@
       <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="42" t="s">
-        <v>490</v>
-      </c>
-      <c r="D7" s="42" t="s">
+      <c r="C7" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="E7" s="67" t="s">
-        <v>492</v>
-      </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="69"/>
+      <c r="E7" s="62" t="s">
+        <v>491</v>
+      </c>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="64"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -3681,15 +3657,15 @@
       <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="70" t="s">
-        <v>497</v>
-      </c>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="72"/>
+      <c r="C8" s="65" t="s">
+        <v>496</v>
+      </c>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="67"/>
       <c r="J8" s="11" t="s">
         <v>16</v>
       </c>
@@ -3705,23 +3681,23 @@
       <c r="B9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="63" t="s">
-        <v>493</v>
-      </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
+      <c r="C9" s="58" t="s">
+        <v>492</v>
+      </c>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
       <c r="F9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="63" t="s">
-        <v>498</v>
-      </c>
-      <c r="H9" s="64"/>
+      <c r="G9" s="58" t="s">
+        <v>497</v>
+      </c>
+      <c r="H9" s="59"/>
       <c r="I9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="73"/>
-      <c r="K9" s="74"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="53"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -3732,7 +3708,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>21</v>
@@ -3760,18 +3736,18 @@
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="76"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="76"/>
-      <c r="K11" s="77"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="70"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -3786,12 +3762,12 @@
         <v>5</v>
       </c>
       <c r="E12" s="22"/>
-      <c r="F12" s="78" t="s">
+      <c r="F12" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="79"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="81"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
       <c r="J12" s="24" t="s">
         <v>25</v>
       </c>
@@ -3812,12 +3788,12 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="82" t="s">
+      <c r="H13" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="83"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="47"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="77"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -3829,13 +3805,13 @@
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="62"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="57"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -3845,36 +3821,36 @@
       <c r="B15" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="46"/>
-      <c r="H15" s="60"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="73"/>
-      <c r="K15" s="74"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="53"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="1:14" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="92" t="s">
+      <c r="B16" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="93"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
       <c r="K16" s="27" t="s">
         <v>27</v>
       </c>
@@ -3888,7 +3864,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D17" s="30" t="s">
         <v>1</v>
@@ -3896,15 +3872,15 @@
       <c r="E17" s="29" t="s">
         <v>448</v>
       </c>
-      <c r="F17" s="84" t="s">
+      <c r="F17" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="85"/>
-      <c r="H17" s="86" t="s">
-        <v>494</v>
-      </c>
-      <c r="I17" s="87"/>
-      <c r="J17" s="88"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44" t="s">
+        <v>493</v>
+      </c>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
       <c r="K17" s="31" t="s">
         <v>461</v>
       </c>
@@ -3918,7 +3894,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D18" s="30" t="s">
         <v>1</v>
@@ -3926,15 +3902,15 @@
       <c r="E18" s="29" t="s">
         <v>446</v>
       </c>
-      <c r="F18" s="84" t="s">
+      <c r="F18" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="85"/>
-      <c r="H18" s="86" t="s">
-        <v>495</v>
-      </c>
-      <c r="I18" s="87"/>
-      <c r="J18" s="88"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44" t="s">
+        <v>494</v>
+      </c>
+      <c r="I18" s="45"/>
+      <c r="J18" s="46"/>
       <c r="K18" s="31" t="s">
         <v>461</v>
       </c>
@@ -3952,13 +3928,13 @@
         <v>1</v>
       </c>
       <c r="E19" s="32"/>
-      <c r="F19" s="84" t="s">
+      <c r="F19" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="85"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="91"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="49"/>
       <c r="K19" s="31"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -4084,16 +4060,13 @@
     <protectedRange sqref="J5:K5" name="input"/>
   </protectedRanges>
   <mergeCells count="31">
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
     <mergeCell ref="E14:K14"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:K5"/>
@@ -4108,13 +4081,16 @@
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="J13:K13"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C12">
@@ -4128,64 +4104,64 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14 D6:D7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14 D6:D7" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT(C6)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:K5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:K5" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT(G5)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1"/>
+    <hyperlink ref="C8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>工作表2!$A$2:$A$8</xm:f>
           </x14:formula1>
           <xm:sqref>E5</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>工作表2!$B$2:$B$28</xm:f>
           </x14:formula1>
           <xm:sqref>F4 F13</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>工作表2!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>G4 G13</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
           <x14:formula1>
             <xm:f>工作表2!$D$2:$D$3</xm:f>
           </x14:formula1>
           <xm:sqref>G5:I5</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
             <xm:f>工作表3!$A$1:$W$1</xm:f>
           </x14:formula1>
           <xm:sqref>C14 C6:C7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007000000}">
           <x14:formula1>
             <xm:f>工作表2!$G$2:$G$3</xm:f>
           </x14:formula1>
           <xm:sqref>K8</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000008000000}">
           <x14:formula1>
             <xm:f>工作表2!$H$2:$H$17</xm:f>
           </x14:formula1>
           <xm:sqref>K12 E17:E19</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000009000000}">
           <x14:formula1>
             <xm:f>工作表2!$I$2:$I$3</xm:f>
           </x14:formula1>
@@ -4198,7 +4174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4496,7 +4472,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5765,7 +5741,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:W1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:W1" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$A$1:$W$1</formula1>
     </dataValidation>
   </dataValidations>
